--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_costs_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_costs_users.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,17 +367,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>mean_visit_costs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_exposed</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>se_costs</t>
+          <t>sd_visit_costs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>se_visit_costs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ci_lower</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ci_upper</t>
         </is>
       </c>
     </row>
@@ -391,13 +406,22 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>267.4260983171749</v>
+        <v>5494510.779550237</v>
       </c>
       <c r="D2">
-        <v>5485444.128681892</v>
+        <v>267.8681152276832</v>
       </c>
       <c r="E2">
-        <v>6.078672600721845E-05</v>
+        <v>341.0245105564662</v>
+      </c>
+      <c r="F2">
+        <v>0.1454859584234157</v>
+      </c>
+      <c r="G2">
+        <v>267.582967926103</v>
+      </c>
+      <c r="H2">
+        <v>268.1532625292634</v>
       </c>
     </row>
     <row r="3">
@@ -410,13 +434,22 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>177.5685817925271</v>
+        <v>3650312.155918934</v>
       </c>
       <c r="D3">
-        <v>3642286.749728315</v>
+        <v>177.9598359944878</v>
       </c>
       <c r="E3">
-        <v>6.745706401948583E-05</v>
+        <v>258.6831434647466</v>
+      </c>
+      <c r="F3">
+        <v>0.1353951561403139</v>
+      </c>
+      <c r="G3">
+        <v>177.6944662767808</v>
+      </c>
+      <c r="H3">
+        <v>178.2252057121949</v>
       </c>
     </row>
     <row r="4">
@@ -429,13 +462,22 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>117.5850380652402</v>
+        <v>2408903.593355643</v>
       </c>
       <c r="D4">
-        <v>2411904.300794208</v>
+        <v>117.4387477259966</v>
       </c>
       <c r="E4">
-        <v>9.207607527184541E-05</v>
+        <v>223.5488974341424</v>
+      </c>
+      <c r="F4">
+        <v>0.144033270619239</v>
+      </c>
+      <c r="G4">
+        <v>117.1564475611644</v>
+      </c>
+      <c r="H4">
+        <v>117.7210478908289</v>
       </c>
     </row>
     <row r="5">
@@ -448,13 +490,22 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>83.8142557477736</v>
+        <v>1714228.064076897</v>
       </c>
       <c r="D5">
-        <v>1719198.013898332</v>
+        <v>83.57196100218881</v>
       </c>
       <c r="E5">
-        <v>0.0001485117756904702</v>
+        <v>254.5423912388175</v>
+      </c>
+      <c r="F5">
+        <v>0.1944132315879659</v>
+      </c>
+      <c r="G5">
+        <v>83.19091780111509</v>
+      </c>
+      <c r="H5">
+        <v>83.95300420326254</v>
       </c>
     </row>
     <row r="6">
@@ -467,13 +518,22 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>64.48916460712074</v>
+        <v>1317345.991485735</v>
       </c>
       <c r="D6">
-        <v>1322801.744421261</v>
+        <v>64.22318601237009</v>
       </c>
       <c r="E6">
-        <v>0.000117517367215279</v>
+        <v>154.0006155064422</v>
+      </c>
+      <c r="F6">
+        <v>0.1341752859395036</v>
+      </c>
+      <c r="G6">
+        <v>63.9602070426906</v>
+      </c>
+      <c r="H6">
+        <v>64.48616498204959</v>
       </c>
     </row>
     <row r="7">
@@ -486,13 +546,22 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>52.50025536727367</v>
+        <v>1071367.04528883</v>
       </c>
       <c r="D7">
-        <v>1076885.238093518</v>
+        <v>52.23123270713877</v>
       </c>
       <c r="E7">
-        <v>0.000129684351364122</v>
+        <v>138.8281344321863</v>
+      </c>
+      <c r="F7">
+        <v>0.1341245710017626</v>
+      </c>
+      <c r="G7">
+        <v>51.9683530815479</v>
+      </c>
+      <c r="H7">
+        <v>52.49411233272964</v>
       </c>
     </row>
     <row r="8">
@@ -505,13 +574,22 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>45.26013133024821</v>
+        <v>924180.6154742212</v>
       </c>
       <c r="D8">
-        <v>928375.8138460512</v>
+        <v>45.05560722865743</v>
       </c>
       <c r="E8">
-        <v>0.0001433890430444194</v>
+        <v>132.7342389909722</v>
+      </c>
+      <c r="F8">
+        <v>0.1380716569496382</v>
+      </c>
+      <c r="G8">
+        <v>44.78499139933459</v>
+      </c>
+      <c r="H8">
+        <v>45.32622305798027</v>
       </c>
     </row>
     <row r="9">
@@ -524,13 +602,22 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>39.12847841972516</v>
+        <v>798476.8602301812</v>
       </c>
       <c r="D9">
-        <v>802603.3493454024</v>
+        <v>38.92730402838247</v>
       </c>
       <c r="E9">
-        <v>0.0001528633479267604</v>
+        <v>122.0530357718552</v>
+      </c>
+      <c r="F9">
+        <v>0.1365895324661039</v>
+      </c>
+      <c r="G9">
+        <v>38.65959305827573</v>
+      </c>
+      <c r="H9">
+        <v>39.19501499848921</v>
       </c>
     </row>
     <row r="10">
@@ -543,13 +630,22 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>35.1076427545736</v>
+        <v>715756.4824479452</v>
       </c>
       <c r="D10">
-        <v>720127.9681818136</v>
+        <v>34.89452430030934</v>
       </c>
       <c r="E10">
-        <v>0.0001565718224677443</v>
+        <v>111.7910832277457</v>
+      </c>
+      <c r="F10">
+        <v>0.1321370233911311</v>
+      </c>
+      <c r="G10">
+        <v>34.63554005548803</v>
+      </c>
+      <c r="H10">
+        <v>35.15350854513066</v>
       </c>
     </row>
     <row r="11">
@@ -562,13 +658,22 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>33.8655521671895</v>
+        <v>690340.4040947576</v>
       </c>
       <c r="D11">
-        <v>694650.206053391</v>
+        <v>33.65544091725612</v>
       </c>
       <c r="E11">
-        <v>0.0001611345949869987</v>
+        <v>111.0183118758652</v>
+      </c>
+      <c r="F11">
+        <v>0.1336173865453938</v>
+      </c>
+      <c r="G11">
+        <v>33.39355519275735</v>
+      </c>
+      <c r="H11">
+        <v>33.91732664175489</v>
       </c>
     </row>
     <row r="12">
@@ -581,13 +686,22 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>31.49456900304011</v>
+        <v>642291.4941806889</v>
       </c>
       <c r="D12">
-        <v>646016.5993903588</v>
+        <v>31.31296285982297</v>
       </c>
       <c r="E12">
-        <v>0.0001761698577487557</v>
+        <v>114.1730840132139</v>
+      </c>
+      <c r="F12">
+        <v>0.1424615439923751</v>
+      </c>
+      <c r="G12">
+        <v>31.03374283823963</v>
+      </c>
+      <c r="H12">
+        <v>31.59218288140632</v>
       </c>
     </row>
     <row r="13">
@@ -600,13 +714,22 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>32.45445208232656</v>
+        <v>661816.1480086134</v>
       </c>
       <c r="D13">
-        <v>665705.7211126825</v>
+        <v>32.26482780853225</v>
       </c>
       <c r="E13">
-        <v>0.0001692105147432927</v>
+        <v>112.1190195420089</v>
+      </c>
+      <c r="F13">
+        <v>0.1378194814447675</v>
+      </c>
+      <c r="G13">
+        <v>31.99470609451877</v>
+      </c>
+      <c r="H13">
+        <v>32.53494952254572</v>
       </c>
     </row>
     <row r="14">
@@ -619,13 +742,22 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>27.73856503742267</v>
+        <v>565143.902482948</v>
       </c>
       <c r="D14">
-        <v>568973.4460476139</v>
+        <v>27.55186732073654</v>
       </c>
       <c r="E14">
-        <v>0.000171777982195671</v>
+        <v>96.98681602937779</v>
+      </c>
+      <c r="F14">
+        <v>0.1290129123185755</v>
+      </c>
+      <c r="G14">
+        <v>27.29900611749952</v>
+      </c>
+      <c r="H14">
+        <v>27.80472852397357</v>
       </c>
     </row>
     <row r="15">
@@ -638,13 +770,22 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>27.96628581828667</v>
+        <v>570019.4803578487</v>
       </c>
       <c r="D15">
-        <v>573644.4547046963</v>
+        <v>27.78956124989512</v>
       </c>
       <c r="E15">
-        <v>0.0001733743893080069</v>
+        <v>98.8123397926682</v>
+      </c>
+      <c r="F15">
+        <v>0.1308779049058185</v>
+      </c>
+      <c r="G15">
+        <v>27.53304472522613</v>
+      </c>
+      <c r="H15">
+        <v>28.04607777456411</v>
       </c>
     </row>
     <row r="16">
@@ -657,13 +798,22 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>26.02605865231817</v>
+        <v>530477.4139324977</v>
       </c>
       <c r="D16">
-        <v>533846.5150763502</v>
+        <v>25.86180840154532</v>
       </c>
       <c r="E16">
-        <v>0.0001905700229540567</v>
+        <v>101.1820955838114</v>
+      </c>
+      <c r="F16">
+        <v>0.138921742159692</v>
+      </c>
+      <c r="G16">
+        <v>25.5895261689884</v>
+      </c>
+      <c r="H16">
+        <v>26.13409063410225</v>
       </c>
     </row>
     <row r="17">
@@ -676,13 +826,22 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>25.82319427292195</v>
+        <v>526594.4139094448</v>
       </c>
       <c r="D17">
-        <v>529685.360926175</v>
+        <v>25.67250457826857</v>
       </c>
       <c r="E17">
-        <v>0.0001879273448939944</v>
+        <v>98.93468603581438</v>
+      </c>
+      <c r="F17">
+        <v>0.1363359711274183</v>
+      </c>
+      <c r="G17">
+        <v>25.4052903708749</v>
+      </c>
+      <c r="H17">
+        <v>25.93971878566223</v>
       </c>
     </row>
     <row r="18">
@@ -695,13 +854,22 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>25.40884620076964</v>
+        <v>518320.9729554538</v>
       </c>
       <c r="D18">
-        <v>521186.2532701868</v>
+        <v>25.26915819790629</v>
       </c>
       <c r="E18">
-        <v>0.0001913877417079292</v>
+        <v>99.3057675240652</v>
+      </c>
+      <c r="F18">
+        <v>0.1379351912235922</v>
+      </c>
+      <c r="G18">
+        <v>24.99880955959768</v>
+      </c>
+      <c r="H18">
+        <v>25.53950683621489</v>
       </c>
     </row>
     <row r="19">
@@ -714,13 +882,22 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>23.42688711634395</v>
+        <v>477801.265396152</v>
       </c>
       <c r="D19">
-        <v>480532.3085304471</v>
+        <v>23.29374343779993</v>
       </c>
       <c r="E19">
-        <v>0.0002027210744967073</v>
+        <v>96.92569563607435</v>
+      </c>
+      <c r="F19">
+        <v>0.1402217163964639</v>
+      </c>
+      <c r="G19">
+        <v>23.01891322761199</v>
+      </c>
+      <c r="H19">
+        <v>23.56857364798786</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +910,22 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>22.56575520825327</v>
+        <v>459989.4492114071</v>
       </c>
       <c r="D20">
-        <v>462868.770831691</v>
+        <v>22.42538266436267</v>
       </c>
       <c r="E20">
-        <v>0.0002126500982887961</v>
+        <v>98.02304497108609</v>
+      </c>
+      <c r="F20">
+        <v>0.1445287524891129</v>
+      </c>
+      <c r="G20">
+        <v>22.14211076938199</v>
+      </c>
+      <c r="H20">
+        <v>22.70865455934335</v>
       </c>
     </row>
     <row r="21">
@@ -752,13 +938,22 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>22.01925179730982</v>
+        <v>448839.4741488203</v>
       </c>
       <c r="D21">
-        <v>451658.8928664189</v>
+        <v>21.88179963674046</v>
       </c>
       <c r="E21">
-        <v>0.0001996507636552331</v>
+        <v>89.71309572086312</v>
+      </c>
+      <c r="F21">
+        <v>0.1339091707570918</v>
+      </c>
+      <c r="G21">
+        <v>21.61934177709739</v>
+      </c>
+      <c r="H21">
+        <v>22.14425749638353</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +966,22 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>21.24468693439529</v>
+        <v>432751.4296834928</v>
       </c>
       <c r="D22">
-        <v>435771.0183983162</v>
+        <v>21.09747609611412</v>
       </c>
       <c r="E22">
-        <v>0.0002193424109273715</v>
+        <v>94.27473583690006</v>
+      </c>
+      <c r="F22">
+        <v>0.1433098589299238</v>
+      </c>
+      <c r="G22">
+        <v>20.81659314837721</v>
+      </c>
+      <c r="H22">
+        <v>21.37835904385103</v>
       </c>
     </row>
     <row r="23">
@@ -790,13 +994,22 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>19.51858614770136</v>
+        <v>397724.8638907074</v>
       </c>
       <c r="D23">
-        <v>400365.2390616502</v>
+        <v>19.38986270918036</v>
       </c>
       <c r="E23">
-        <v>0.000214745170033331</v>
+        <v>85.47056761204468</v>
+      </c>
+      <c r="F23">
+        <v>0.1355268103323115</v>
+      </c>
+      <c r="G23">
+        <v>19.12423423362126</v>
+      </c>
+      <c r="H23">
+        <v>19.65549118473945</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +1022,22 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>19.34598857111079</v>
+        <v>393998.8711241712</v>
       </c>
       <c r="D24">
-        <v>396824.9175706246</v>
+        <v>19.20821329583518</v>
       </c>
       <c r="E24">
-        <v>0.0002359537199074573</v>
+        <v>92.65944133944886</v>
+      </c>
+      <c r="F24">
+        <v>0.1476189760981487</v>
+      </c>
+      <c r="G24">
+        <v>18.91888453042783</v>
+      </c>
+      <c r="H24">
+        <v>19.49754206124254</v>
       </c>
     </row>
     <row r="25">
@@ -828,13 +1050,22 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>17.58526776693666</v>
+        <v>358037.2994391443</v>
       </c>
       <c r="D25">
-        <v>360709.0124354047</v>
+        <v>17.45501654832022</v>
       </c>
       <c r="E25">
-        <v>0.0002222982628316175</v>
+        <v>79.57939447903702</v>
+      </c>
+      <c r="F25">
+        <v>0.1329953613873028</v>
+      </c>
+      <c r="G25">
+        <v>17.19434954868873</v>
+      </c>
+      <c r="H25">
+        <v>17.71568354795171</v>
       </c>
     </row>
     <row r="26">
@@ -847,13 +1078,22 @@
         <v>1</v>
       </c>
       <c r="C26">
+        <v>6009021.335224808</v>
+      </c>
+      <c r="D26">
         <v>290.4171540875167</v>
       </c>
-      <c r="D26">
-        <v>6009021.335224808</v>
-      </c>
       <c r="E26">
-        <v>6.504361560634642E-05</v>
+        <v>390.848473898697</v>
+      </c>
+      <c r="F26">
+        <v>0.1594434002917461</v>
+      </c>
+      <c r="G26">
+        <v>290.1046507024265</v>
+      </c>
+      <c r="H26">
+        <v>290.729657472607</v>
       </c>
     </row>
     <row r="27">
@@ -866,13 +1106,22 @@
         <v>2</v>
       </c>
       <c r="C27">
+        <v>3874800.386053412</v>
+      </c>
+      <c r="D27">
         <v>187.2698461192505</v>
       </c>
-      <c r="D27">
-        <v>3874800.386053412</v>
-      </c>
       <c r="E27">
-        <v>7.406950689113474E-05</v>
+        <v>287.0045538965547</v>
+      </c>
+      <c r="F27">
+        <v>0.1458022146012464</v>
+      </c>
+      <c r="G27">
+        <v>186.9840789405013</v>
+      </c>
+      <c r="H27">
+        <v>187.5556132979997</v>
       </c>
     </row>
     <row r="28">
@@ -885,13 +1134,22 @@
         <v>3</v>
       </c>
       <c r="C28">
+        <v>2562622.612112426</v>
+      </c>
+      <c r="D28">
         <v>123.8520425360024</v>
       </c>
-      <c r="D28">
-        <v>2562622.612112426</v>
-      </c>
       <c r="E28">
-        <v>9.818652249535992E-05</v>
+        <v>251.6150027512948</v>
+      </c>
+      <c r="F28">
+        <v>0.1571788857569936</v>
+      </c>
+      <c r="G28">
+        <v>123.5439774352848</v>
+      </c>
+      <c r="H28">
+        <v>124.16010763672</v>
       </c>
     </row>
     <row r="29">
@@ -904,13 +1162,22 @@
         <v>4</v>
       </c>
       <c r="C29">
+        <v>1811263.543490788</v>
+      </c>
+      <c r="D29">
         <v>87.53871458560667</v>
       </c>
-      <c r="D29">
-        <v>1811263.543490788</v>
-      </c>
       <c r="E29">
-        <v>0.0001371448147691625</v>
+        <v>248.405403170181</v>
+      </c>
+      <c r="F29">
+        <v>0.1845738686960687</v>
+      </c>
+      <c r="G29">
+        <v>87.17695620873241</v>
+      </c>
+      <c r="H29">
+        <v>87.90047296248093</v>
       </c>
     </row>
     <row r="30">
@@ -923,13 +1190,22 @@
         <v>5</v>
       </c>
       <c r="C30">
+        <v>1408120.427261455</v>
+      </c>
+      <c r="D30">
         <v>68.05473042682594</v>
       </c>
-      <c r="D30">
-        <v>1408120.427261455</v>
-      </c>
       <c r="E30">
-        <v>0.0001159746458899538</v>
+        <v>163.3062679220578</v>
+      </c>
+      <c r="F30">
+        <v>0.1376204439531808</v>
+      </c>
+      <c r="G30">
+        <v>67.78499908129072</v>
+      </c>
+      <c r="H30">
+        <v>68.32446177236116</v>
       </c>
     </row>
     <row r="31">
@@ -942,13 +1218,22 @@
         <v>6</v>
       </c>
       <c r="C31">
+        <v>1140221.413694534</v>
+      </c>
+      <c r="D31">
         <v>55.10711969912204</v>
       </c>
-      <c r="D31">
-        <v>1140221.413694534</v>
-      </c>
       <c r="E31">
-        <v>0.000130500413048711</v>
+        <v>148.7993654541219</v>
+      </c>
+      <c r="F31">
+        <v>0.1393498426735711</v>
+      </c>
+      <c r="G31">
+        <v>54.83399873630766</v>
+      </c>
+      <c r="H31">
+        <v>55.38024066193643</v>
       </c>
     </row>
     <row r="32">
@@ -961,13 +1246,22 @@
         <v>7</v>
       </c>
       <c r="C32">
+        <v>992482.877903262</v>
+      </c>
+      <c r="D32">
         <v>47.96688791760969</v>
       </c>
-      <c r="D32">
-        <v>992482.877903262</v>
-      </c>
       <c r="E32">
-        <v>0.0001507969245506519</v>
+        <v>149.6633656569921</v>
+      </c>
+      <c r="F32">
+        <v>0.1502290759439532</v>
+      </c>
+      <c r="G32">
+        <v>47.67244398024463</v>
+      </c>
+      <c r="H32">
+        <v>48.26133185497475</v>
       </c>
     </row>
     <row r="33">
@@ -980,13 +1274,22 @@
         <v>8</v>
       </c>
       <c r="C33">
+        <v>864152.9207462566</v>
+      </c>
+      <c r="D33">
         <v>41.76467646543215</v>
       </c>
-      <c r="D33">
-        <v>864152.9207462566</v>
-      </c>
       <c r="E33">
-        <v>0.0001607193075952313</v>
+        <v>138.8860590787351</v>
+      </c>
+      <c r="F33">
+        <v>0.1494043883216443</v>
+      </c>
+      <c r="G33">
+        <v>41.47184883504376</v>
+      </c>
+      <c r="H33">
+        <v>42.05750409582053</v>
       </c>
     </row>
     <row r="34">
@@ -999,13 +1302,22 @@
         <v>9</v>
       </c>
       <c r="C34">
+        <v>773262.6539671132</v>
+      </c>
+      <c r="D34">
         <v>37.37193243280234</v>
       </c>
-      <c r="D34">
-        <v>773262.6539671132</v>
-      </c>
       <c r="E34">
-        <v>0.000161343611148394</v>
+        <v>124.7609889572451</v>
+      </c>
+      <c r="F34">
+        <v>0.141878076138658</v>
+      </c>
+      <c r="G34">
+        <v>37.09385607810966</v>
+      </c>
+      <c r="H34">
+        <v>37.65000878749502</v>
       </c>
     </row>
     <row r="35">
@@ -1018,13 +1330,22 @@
         <v>10</v>
       </c>
       <c r="C35">
+        <v>743612.6480470877</v>
+      </c>
+      <c r="D35">
         <v>35.93894195771532</v>
       </c>
-      <c r="D35">
-        <v>743612.6480470877</v>
-      </c>
       <c r="E35">
-        <v>0.0001628680818664278</v>
+        <v>121.1107656390442</v>
+      </c>
+      <c r="F35">
+        <v>0.1404459970700682</v>
+      </c>
+      <c r="G35">
+        <v>35.66367241363338</v>
+      </c>
+      <c r="H35">
+        <v>36.21421150179727</v>
       </c>
     </row>
     <row r="36">
@@ -1037,13 +1358,22 @@
         <v>11</v>
       </c>
       <c r="C36">
+        <v>695702.4583912443</v>
+      </c>
+      <c r="D36">
         <v>33.62343329907903</v>
       </c>
-      <c r="D36">
-        <v>695702.4583912443</v>
-      </c>
       <c r="E36">
-        <v>0.0001841950018952039</v>
+        <v>128.1449156418733</v>
+      </c>
+      <c r="F36">
+        <v>0.1536348039329487</v>
+      </c>
+      <c r="G36">
+        <v>33.32231409271863</v>
+      </c>
+      <c r="H36">
+        <v>33.92455250543944</v>
       </c>
     </row>
     <row r="37">
@@ -1056,13 +1386,22 @@
         <v>12</v>
       </c>
       <c r="C37">
+        <v>717856.5191662922</v>
+      </c>
+      <c r="D37">
         <v>34.69414330705582</v>
       </c>
-      <c r="D37">
-        <v>717856.5191662922</v>
-      </c>
       <c r="E37">
-        <v>0.000171088427759519</v>
+        <v>122.816943221082</v>
+      </c>
+      <c r="F37">
+        <v>0.1449570892296235</v>
+      </c>
+      <c r="G37">
+        <v>34.41003215382675</v>
+      </c>
+      <c r="H37">
+        <v>34.9782544602849</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1414,22 @@
         <v>13</v>
       </c>
       <c r="C38">
+        <v>606753.0856206736</v>
+      </c>
+      <c r="D38">
         <v>29.32449304628455</v>
       </c>
-      <c r="D38">
-        <v>606753.0856206736</v>
-      </c>
       <c r="E38">
-        <v>0.0001795449073796946</v>
+        <v>108.9394265601077</v>
+      </c>
+      <c r="F38">
+        <v>0.1398553511730301</v>
+      </c>
+      <c r="G38">
+        <v>29.05038104813454</v>
+      </c>
+      <c r="H38">
+        <v>29.59860504443455</v>
       </c>
     </row>
     <row r="39">
@@ -1094,13 +1442,22 @@
         <v>14</v>
       </c>
       <c r="C39">
+        <v>621221.2767165386</v>
+      </c>
+      <c r="D39">
         <v>30.023743497972</v>
       </c>
-      <c r="D39">
-        <v>621221.2767165386</v>
-      </c>
       <c r="E39">
-        <v>0.000184648204564553</v>
+        <v>114.7073933830082</v>
+      </c>
+      <c r="F39">
+        <v>0.1455352680227454</v>
+      </c>
+      <c r="G39">
+        <v>29.73849905840637</v>
+      </c>
+      <c r="H39">
+        <v>30.30898793753762</v>
       </c>
     </row>
     <row r="40">
@@ -1113,13 +1470,22 @@
         <v>15</v>
       </c>
       <c r="C40">
+        <v>578977.5324440817</v>
+      </c>
+      <c r="D40">
         <v>27.98209523194054</v>
       </c>
-      <c r="D40">
-        <v>578977.5324440817</v>
-      </c>
       <c r="E40">
-        <v>0.0001977023682123915</v>
+        <v>114.4652293059617</v>
+      </c>
+      <c r="F40">
+        <v>0.1504328651318024</v>
+      </c>
+      <c r="G40">
+        <v>27.68725161781322</v>
+      </c>
+      <c r="H40">
+        <v>28.27693884606786</v>
       </c>
     </row>
     <row r="41">
@@ -1132,13 +1498,22 @@
         <v>16</v>
       </c>
       <c r="C41">
+        <v>569198.2585856941</v>
+      </c>
+      <c r="D41">
         <v>27.50946105000697</v>
       </c>
-      <c r="D41">
-        <v>569198.2585856941</v>
-      </c>
       <c r="E41">
-        <v>0.0001928011551599794</v>
+        <v>109.7420817703705</v>
+      </c>
+      <c r="F41">
+        <v>0.1454592731144644</v>
+      </c>
+      <c r="G41">
+        <v>27.22436550724625</v>
+      </c>
+      <c r="H41">
+        <v>27.79455659276768</v>
       </c>
     </row>
     <row r="42">
@@ -1151,13 +1526,22 @@
         <v>17</v>
       </c>
       <c r="C42">
+        <v>569573.8716341355</v>
+      </c>
+      <c r="D42">
         <v>27.52761450070733</v>
       </c>
-      <c r="D42">
-        <v>569573.8716341355</v>
-      </c>
       <c r="E42">
-        <v>0.0001950803225493022</v>
+        <v>111.112654594042</v>
+      </c>
+      <c r="F42">
+        <v>0.1472273496926264</v>
+      </c>
+      <c r="G42">
+        <v>27.23905358456725</v>
+      </c>
+      <c r="H42">
+        <v>27.81617541684741</v>
       </c>
     </row>
     <row r="43">
@@ -1170,13 +1554,22 @@
         <v>18</v>
       </c>
       <c r="C43">
+        <v>516302.7408298189</v>
+      </c>
+      <c r="D43">
         <v>24.95301052775694</v>
       </c>
-      <c r="D43">
-        <v>516302.7408298189</v>
-      </c>
       <c r="E43">
-        <v>0.0002045131645238948</v>
+        <v>105.5907073794666</v>
+      </c>
+      <c r="F43">
+        <v>0.1469513174847074</v>
+      </c>
+      <c r="G43">
+        <v>24.66499056280184</v>
+      </c>
+      <c r="H43">
+        <v>25.24103049271204</v>
       </c>
     </row>
     <row r="44">
@@ -1189,13 +1582,22 @@
         <v>19</v>
       </c>
       <c r="C44">
+        <v>514733.9971963592</v>
+      </c>
+      <c r="D44">
         <v>24.87719284695564</v>
       </c>
-      <c r="D44">
-        <v>514733.9971963592</v>
-      </c>
       <c r="E44">
-        <v>0.0003439701523377018</v>
+        <v>177.0531314290258</v>
+      </c>
+      <c r="F44">
+        <v>0.2467812646647009</v>
+      </c>
+      <c r="G44">
+        <v>24.39350931879994</v>
+      </c>
+      <c r="H44">
+        <v>25.36087637511134</v>
       </c>
     </row>
     <row r="45">
@@ -1208,13 +1610,22 @@
         <v>20</v>
       </c>
       <c r="C45">
+        <v>487329.5357204647</v>
+      </c>
+      <c r="D45">
         <v>23.55272996570802</v>
       </c>
-      <c r="D45">
-        <v>487329.5357204647</v>
-      </c>
       <c r="E45">
-        <v>0.0002082477173675609</v>
+        <v>101.48526341958</v>
+      </c>
+      <c r="F45">
+        <v>0.1453756322551107</v>
+      </c>
+      <c r="G45">
+        <v>23.26779825458111</v>
+      </c>
+      <c r="H45">
+        <v>23.83766167683494</v>
       </c>
     </row>
     <row r="46">
@@ -1227,13 +1638,22 @@
         <v>21</v>
       </c>
       <c r="C46">
+        <v>470884.9898333896</v>
+      </c>
+      <c r="D46">
         <v>22.75796190775649</v>
       </c>
-      <c r="D46">
-        <v>470884.9898333896</v>
-      </c>
       <c r="E46">
-        <v>0.0002214378143608959</v>
+        <v>104.2717429640585</v>
+      </c>
+      <c r="F46">
+        <v>0.1519529758233192</v>
+      </c>
+      <c r="G46">
+        <v>22.46013878227173</v>
+      </c>
+      <c r="H46">
+        <v>23.05578503324126</v>
       </c>
     </row>
     <row r="47">
@@ -1246,13 +1666,22 @@
         <v>22</v>
       </c>
       <c r="C47">
+        <v>427395.6459560183</v>
+      </c>
+      <c r="D47">
         <v>20.65611357382525</v>
       </c>
-      <c r="D47">
-        <v>427395.6459560183</v>
-      </c>
       <c r="E47">
-        <v>0.0002147033587494227</v>
+        <v>91.76328070163625</v>
+      </c>
+      <c r="F47">
+        <v>0.1403634018414607</v>
+      </c>
+      <c r="G47">
+        <v>20.38100558237357</v>
+      </c>
+      <c r="H47">
+        <v>20.93122156527693</v>
       </c>
     </row>
     <row r="48">
@@ -1265,13 +1694,22 @@
         <v>23</v>
       </c>
       <c r="C48">
+        <v>420884.8489444911</v>
+      </c>
+      <c r="D48">
         <v>20.34144550502591</v>
       </c>
-      <c r="D48">
-        <v>420884.8489444911</v>
-      </c>
       <c r="E48">
-        <v>0.0002323265195898762</v>
+        <v>97.7827121033844</v>
+      </c>
+      <c r="F48">
+        <v>0.1507233133229168</v>
+      </c>
+      <c r="G48">
+        <v>20.04603238974262</v>
+      </c>
+      <c r="H48">
+        <v>20.63685862030919</v>
       </c>
     </row>
     <row r="49">
@@ -1284,13 +1722,22 @@
         <v>24</v>
       </c>
       <c r="C49">
+        <v>381732.1198249586</v>
+      </c>
+      <c r="D49">
         <v>18.44918659441103</v>
       </c>
-      <c r="D49">
-        <v>381732.1198249586</v>
-      </c>
       <c r="E49">
-        <v>0.0002230547600731697</v>
+        <v>85.14716639977858</v>
+      </c>
+      <c r="F49">
+        <v>0.1378132097159516</v>
+      </c>
+      <c r="G49">
+        <v>18.17907681032989</v>
+      </c>
+      <c r="H49">
+        <v>18.71929637849217</v>
       </c>
     </row>
   </sheetData>
